--- a/data/trans_bre/IP1006-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Clase-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,0</t>
+          <t>-4,92; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,0</t>
+          <t>-3,53; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,0</t>
+          <t>-4,25; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,33</t>
+          <t>-2,47; 0,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,05</t>
+          <t>-1,14; 2,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -0,49</t>
+          <t>-4,89; -0,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,54</t>
+          <t>-0,43; 4,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,0</t>
+          <t>-5,85; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,47</t>
+          <t>-0,51; 0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; -0,09</t>
+          <t>-1,42; -0,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,73</t>
+          <t>-0,35; 0,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,93</t>
+          <t>-100,0; 77,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-83,12; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1006-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Clase-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,0</t>
+          <t>-3,75; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,0</t>
+          <t>-3,52; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,0</t>
+          <t>-3,86; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,32</t>
+          <t>-2,32; 0,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,02</t>
+          <t>-1,14; 2,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,48</t>
+          <t>-5,04; -0,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,02</t>
+          <t>-0,43; 3,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 0,0</t>
+          <t>-6,1; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,41</t>
+          <t>-0,53; 0,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; -0,07</t>
+          <t>-1,44; -0,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,7</t>
+          <t>-0,36; 0,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,25</t>
+          <t>-100,0; 45,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_bre/IP1006-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Clase-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,0</t>
+          <t>-3,53; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,0</t>
+          <t>-3,5; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,0</t>
+          <t>-4,76; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,35</t>
+          <t>-2,51; 0,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,26</t>
+          <t>-1,14; 2,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,48</t>
+          <t>-5,13; -0,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,65</t>
+          <t>-0,45; 3,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 0,0</t>
+          <t>-6,05; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,49</t>
+          <t>-0,5; 0,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; -0,08</t>
+          <t>-1,44; -0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,69</t>
+          <t>-0,35; 0,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 45,24</t>
+          <t>-100,0; 30,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,12; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1006-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,109 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7433201584128321</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,53; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>-3.5293435333567</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,08</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +713,143 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-5,69%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-73,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.6994137413969059</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8133961718757006</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.8399046729669025</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,04; 0,64</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,51; 0,33</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,19</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.504719693046739</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.761851626419475</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.07635539553077</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>247,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,14; 2,05</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,13; -0,49</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,45; 3,54</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C13" s="5" t="n">
+        <v>-0.01929847391777596</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.8686526226046145</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.268424696963368</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.05692475808503684</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.7299708009416446</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.040546026562982</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.50545245043613</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,24</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-6,05; 0,0</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6418129774322811</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.3254021935438169</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.194702606749241</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +857,209 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-5,66%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-75,81%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>41,32%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.09053202183269532</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.803334156561983</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.084416213385083</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.1600114380917214</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2.478997701984303</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,5; 0,47</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,44; -0,09</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,35; 0,73</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 30,93</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-83,12; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.138121068484502</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.125599209857737</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.4456838586938943</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.050603448094821</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.4864453753890332</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.538842915292881</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.6993325924496401</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-1.0904431067143</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="n">
+        <v>-6.049254917240368</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>4.239773940038487</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.01736426217486434</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.6256741414149877</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.1163757672112562</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.05660803094185494</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.7581141713916177</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.4131799702758021</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.5042455617484347</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.443584352049641</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.351025280616983</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.8312083706229739</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.4748180901641673</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-0.08744339970405529</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.7319355698758598</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="n">
+        <v>0.3093008411987136</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1068,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
